--- a/TestData/Sales_Dimensions.xlsx
+++ b/TestData/Sales_Dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyOlap\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A8DEF-A4EA-4AB9-B808-C5DEB227C1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB83B62-1BF6-4119-87BC-41EDCF0495D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="904" xr2:uid="{0926A686-6C16-458D-B759-A471657F5770}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="904" activeTab="1" xr2:uid="{0926A686-6C16-458D-B759-A471657F5770}"/>
   </bookViews>
   <sheets>
     <sheet name="Measure" sheetId="9" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="266">
   <si>
     <t>Final</t>
   </si>
@@ -631,9 +631,6 @@
     <t>Jun YTD</t>
   </si>
   <si>
-    <t>=Sum(Jan:Feb)</t>
-  </si>
-  <si>
     <t>YTDJul</t>
   </si>
   <si>
@@ -670,36 +667,6 @@
     <t>Oct Dec</t>
   </si>
   <si>
-    <t>=Sum(Jan:Mar)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Apr)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:May)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Jun)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Jul)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Aug)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Sep)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Oct)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Nov)</t>
-  </si>
-  <si>
-    <t>=Sum(Jan:Dec)</t>
-  </si>
-  <si>
     <t>Greg Merchand</t>
   </si>
   <si>
@@ -748,9 +715,6 @@
     <t>Qtr4</t>
   </si>
   <si>
-    <t xml:space="preserve">=Jan </t>
-  </si>
-  <si>
     <t>FY2025</t>
   </si>
   <si>
@@ -790,9 +754,6 @@
     <t>Margin</t>
   </si>
   <si>
-    <t>Profit Margin = "Trading Profit"/"Sales"*100</t>
-  </si>
-  <si>
     <t>Trading Metrics</t>
   </si>
   <si>
@@ -806,13 +767,91 @@
   </si>
   <si>
     <t>Equation</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>HeadCount</t>
+  </si>
+  <si>
+    <t>Head Count</t>
+  </si>
+  <si>
+    <t>SalesDays</t>
+  </si>
+  <si>
+    <t>Sales Days</t>
+  </si>
+  <si>
+    <t>DailySales</t>
+  </si>
+  <si>
+    <t>Avg. Daily Sales</t>
+  </si>
+  <si>
+    <t>"DailySales"="Sales"/"SalesDays"</t>
+  </si>
+  <si>
+    <t>"Profit Margin" = "Trading Profit"/"Sales"*100</t>
+  </si>
+  <si>
+    <t>"YTDJan"="Jan"</t>
+  </si>
+  <si>
+    <t>"YTDFeb"="YTDJan"+"Feb"</t>
+  </si>
+  <si>
+    <t>"YTDMar"="YTDFeb"+"Mar"</t>
+  </si>
+  <si>
+    <t>"YTDApr"="YTDMar"+"Apr"</t>
+  </si>
+  <si>
+    <t>"YTDMay"="YTDApr"+"May"</t>
+  </si>
+  <si>
+    <t>"YTDJun"="Jan"+"Feb"+"Mar"+"Apr"+"May"+"Jun"</t>
+  </si>
+  <si>
+    <t>"YTDJul"="YTDJun"+"Jul"</t>
+  </si>
+  <si>
+    <t>"YTDAug"="YTDJul"+"Aug"</t>
+  </si>
+  <si>
+    <t>"YTDSep"="YTDAug"+"Sep"</t>
+  </si>
+  <si>
+    <t>"YTDOct"="YTDSep"+"Oct"</t>
+  </si>
+  <si>
+    <t>"YTDNov"="YTDOct"+"Nov"</t>
+  </si>
+  <si>
+    <t>"YTDDec"="YTDNov"+"Dec"</t>
+  </si>
+  <si>
+    <t>FirstHalfYr</t>
+  </si>
+  <si>
+    <t>SecondHalfYr</t>
+  </si>
+  <si>
+    <t>YTDSep2</t>
+  </si>
+  <si>
+    <t>Sep YTD2</t>
+  </si>
+  <si>
+    <t>"YTDSep"="YTDAug"+"Sep"+"Sep"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -844,8 +883,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,6 +902,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -938,19 +991,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="42"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1283,19 +1330,19 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F117"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.265625" customWidth="1"/>
-    <col min="6" max="6" width="36.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="47.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1309,13 +1356,13 @@
         <v>180</v>
       </c>
       <c r="E1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1323,16 +1370,16 @@
         <v>4</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1340,16 +1387,16 @@
         <v>5</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1357,13 +1404,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1371,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1385,13 +1432,13 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1399,13 +1446,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1413,13 +1460,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1427,13 +1474,13 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>5</v>
       </c>
@@ -1441,13 +1488,13 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -1455,13 +1502,13 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -1469,13 +1516,13 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -1483,13 +1530,13 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -1497,13 +1544,13 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -1511,13 +1558,13 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1525,13 +1572,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1539,13 +1586,13 @@
         <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -1553,13 +1600,13 @@
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1567,13 +1614,13 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1581,13 +1628,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1595,13 +1642,13 @@
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1609,13 +1656,13 @@
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -1623,13 +1670,13 @@
         <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1637,13 +1684,13 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -1651,13 +1698,13 @@
         <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -1665,13 +1712,13 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -1679,13 +1726,13 @@
         <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -1693,13 +1740,13 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -1707,13 +1754,13 @@
         <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -1721,13 +1768,13 @@
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -1735,13 +1782,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -1749,13 +1796,13 @@
         <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
@@ -1763,13 +1810,13 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
@@ -1777,13 +1824,13 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
@@ -1791,13 +1838,13 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -1805,13 +1852,13 @@
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -1819,13 +1866,13 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>16</v>
       </c>
@@ -1833,13 +1880,13 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
@@ -1847,13 +1894,13 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>18</v>
       </c>
@@ -1864,13 +1911,13 @@
         <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
@@ -1881,13 +1928,13 @@
         <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>18</v>
       </c>
@@ -1898,13 +1945,13 @@
         <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>18</v>
       </c>
@@ -1915,13 +1962,13 @@
         <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>18</v>
       </c>
@@ -1932,13 +1979,13 @@
         <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>18</v>
       </c>
@@ -1949,13 +1996,13 @@
         <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>19</v>
       </c>
@@ -1966,13 +2013,13 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>19</v>
       </c>
@@ -1983,13 +2030,13 @@
         <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>19</v>
       </c>
@@ -2000,13 +2047,13 @@
         <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>19</v>
       </c>
@@ -2017,13 +2064,13 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>20</v>
       </c>
@@ -2034,13 +2081,13 @@
         <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>20</v>
       </c>
@@ -2051,13 +2098,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -2068,13 +2115,13 @@
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
@@ -2085,13 +2132,13 @@
         <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
@@ -2102,13 +2149,13 @@
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -2119,13 +2166,13 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>7</v>
       </c>
@@ -2136,13 +2183,13 @@
         <v>53</v>
       </c>
       <c r="D56" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>22</v>
       </c>
@@ -2153,13 +2200,13 @@
         <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>23</v>
       </c>
@@ -2170,13 +2217,13 @@
         <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>24</v>
       </c>
@@ -2187,13 +2234,13 @@
         <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
@@ -2204,13 +2251,13 @@
         <v>54</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>25</v>
       </c>
@@ -2221,13 +2268,13 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>26</v>
       </c>
@@ -2238,13 +2285,13 @@
         <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>27</v>
       </c>
@@ -2255,13 +2302,13 @@
         <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>27</v>
       </c>
@@ -2272,13 +2319,13 @@
         <v>56</v>
       </c>
       <c r="D64" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>27</v>
       </c>
@@ -2289,13 +2336,13 @@
         <v>57</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>28</v>
       </c>
@@ -2306,13 +2353,13 @@
         <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
@@ -2323,13 +2370,13 @@
         <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -2340,13 +2387,13 @@
         <v>59</v>
       </c>
       <c r="D68" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>29</v>
       </c>
@@ -2357,13 +2404,13 @@
         <v>60</v>
       </c>
       <c r="D69" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>29</v>
       </c>
@@ -2374,13 +2421,13 @@
         <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>29</v>
       </c>
@@ -2391,13 +2438,13 @@
         <v>62</v>
       </c>
       <c r="D71" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>30</v>
       </c>
@@ -2408,13 +2455,13 @@
         <v>63</v>
       </c>
       <c r="D72" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>30</v>
       </c>
@@ -2425,13 +2472,13 @@
         <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>31</v>
       </c>
@@ -2442,13 +2489,13 @@
         <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>31</v>
       </c>
@@ -2459,13 +2506,13 @@
         <v>66</v>
       </c>
       <c r="D75" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>31</v>
       </c>
@@ -2476,13 +2523,13 @@
         <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>31</v>
       </c>
@@ -2493,13 +2540,13 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>31</v>
       </c>
@@ -2510,13 +2557,13 @@
         <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>31</v>
       </c>
@@ -2527,13 +2574,13 @@
         <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>32</v>
       </c>
@@ -2544,13 +2591,13 @@
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>32</v>
       </c>
@@ -2561,13 +2608,13 @@
         <v>71</v>
       </c>
       <c r="D81" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>32</v>
       </c>
@@ -2578,13 +2625,13 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>13</v>
       </c>
@@ -2595,13 +2642,13 @@
         <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>33</v>
       </c>
@@ -2612,13 +2659,13 @@
         <v>74</v>
       </c>
       <c r="D84" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>33</v>
       </c>
@@ -2629,13 +2676,13 @@
         <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>33</v>
       </c>
@@ -2646,13 +2693,13 @@
         <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>33</v>
       </c>
@@ -2663,13 +2710,13 @@
         <v>77</v>
       </c>
       <c r="D87" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>33</v>
       </c>
@@ -2680,13 +2727,13 @@
         <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>34</v>
       </c>
@@ -2697,13 +2744,13 @@
         <v>79</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>34</v>
       </c>
@@ -2714,13 +2761,13 @@
         <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>34</v>
       </c>
@@ -2731,13 +2778,13 @@
         <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>34</v>
       </c>
@@ -2748,13 +2795,13 @@
         <v>82</v>
       </c>
       <c r="D92" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>34</v>
       </c>
@@ -2765,13 +2812,13 @@
         <v>83</v>
       </c>
       <c r="D93" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>34</v>
       </c>
@@ -2782,13 +2829,13 @@
         <v>84</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>34</v>
       </c>
@@ -2799,13 +2846,13 @@
         <v>86</v>
       </c>
       <c r="D95" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>34</v>
       </c>
@@ -2816,13 +2863,13 @@
         <v>87</v>
       </c>
       <c r="D96" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>34</v>
       </c>
@@ -2833,13 +2880,13 @@
         <v>88</v>
       </c>
       <c r="D97" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>34</v>
       </c>
@@ -2850,13 +2897,13 @@
         <v>170</v>
       </c>
       <c r="D98" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>35</v>
       </c>
@@ -2867,13 +2914,13 @@
         <v>89</v>
       </c>
       <c r="D99" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>35</v>
       </c>
@@ -2884,13 +2931,13 @@
         <v>90</v>
       </c>
       <c r="D100" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>35</v>
       </c>
@@ -2901,13 +2948,13 @@
         <v>91</v>
       </c>
       <c r="D101" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>35</v>
       </c>
@@ -2918,13 +2965,13 @@
         <v>92</v>
       </c>
       <c r="D102" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>36</v>
       </c>
@@ -2935,13 +2982,13 @@
         <v>93</v>
       </c>
       <c r="D103" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>36</v>
       </c>
@@ -2952,13 +2999,13 @@
         <v>94</v>
       </c>
       <c r="D104" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>37</v>
       </c>
@@ -2969,13 +3016,13 @@
         <v>95</v>
       </c>
       <c r="D105" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
@@ -2986,13 +3033,13 @@
         <v>96</v>
       </c>
       <c r="D106" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>17</v>
       </c>
@@ -3003,13 +3050,13 @@
         <v>97</v>
       </c>
       <c r="D107" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>17</v>
       </c>
@@ -3020,13 +3067,13 @@
         <v>98</v>
       </c>
       <c r="D108" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>17</v>
       </c>
@@ -3037,13 +3084,13 @@
         <v>99</v>
       </c>
       <c r="D109" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>17</v>
       </c>
@@ -3054,13 +3101,13 @@
         <v>100</v>
       </c>
       <c r="D110" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>17</v>
       </c>
@@ -3071,13 +3118,13 @@
         <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>17</v>
       </c>
@@ -3085,16 +3132,16 @@
         <v>910040</v>
       </c>
       <c r="C112" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D112" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>17</v>
       </c>
@@ -3102,32 +3149,86 @@
         <v>910050</v>
       </c>
       <c r="C113" t="s">
+        <v>231</v>
+      </c>
+      <c r="D113" t="s">
+        <v>218</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C114" t="s">
+        <v>238</v>
+      </c>
+      <c r="D114" t="s">
+        <v>220</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F114" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" t="s">
+        <v>242</v>
+      </c>
+      <c r="D115" t="s">
+        <v>220</v>
+      </c>
+      <c r="E115" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B116" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D113" t="s">
-        <v>229</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A114" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B114" s="11" t="s">
+      <c r="C116" t="s">
+        <v>244</v>
+      </c>
+      <c r="D116" t="s">
+        <v>220</v>
+      </c>
+      <c r="E116" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" t="s">
         <v>246</v>
       </c>
-      <c r="C114" t="s">
-        <v>251</v>
-      </c>
-      <c r="D114" t="s">
-        <v>231</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="D117" t="s">
+        <v>220</v>
+      </c>
+      <c r="E117" t="s">
+        <v>239</v>
+      </c>
+      <c r="F117" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3146,16 +3247,17 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="20.73046875" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3172,7 +3274,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>171</v>
       </c>
@@ -3183,10 +3285,10 @@
         <v>176</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>171</v>
       </c>
@@ -3197,11 +3299,11 @@
         <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>171</v>
       </c>
@@ -3212,10 +3314,10 @@
         <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -3226,10 +3328,10 @@
         <v>105</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -3240,10 +3342,10 @@
         <v>107</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>103</v>
       </c>
@@ -3254,10 +3356,10 @@
         <v>109</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -3265,382 +3367,531 @@
         <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
       <c r="B9" t="s">
         <v>110</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="16" t="s">
         <v>110</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>104</v>
       </c>
       <c r="B10" t="s">
         <v>112</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>104</v>
       </c>
       <c r="B11" t="s">
         <v>117</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="16" t="s">
         <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>106</v>
       </c>
       <c r="B12" t="s">
         <v>118</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="16" t="s">
         <v>118</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>106</v>
       </c>
       <c r="B13" t="s">
         <v>119</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="16" t="s">
         <v>119</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>106</v>
       </c>
       <c r="B14" t="s">
         <v>120</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="16" t="s">
         <v>120</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>108</v>
       </c>
       <c r="B15" t="s">
         <v>121</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="16" t="s">
         <v>121</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
       <c r="B16" t="s">
         <v>122</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>108</v>
       </c>
       <c r="B17" t="s">
         <v>116</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="16" t="s">
         <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>111</v>
       </c>
       <c r="B18" t="s">
         <v>115</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="16" t="s">
         <v>115</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>111</v>
       </c>
       <c r="B19" t="s">
         <v>114</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
       <c r="B20" t="s">
         <v>113</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="16" t="s">
         <v>113</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>182</v>
       </c>
       <c r="B21" t="s">
         <v>178</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="16" t="s">
         <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>182</v>
       </c>
       <c r="B22" t="s">
         <v>184</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="16" t="s">
         <v>185</v>
       </c>
       <c r="D22" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>182</v>
       </c>
       <c r="B23" t="s">
         <v>186</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="16" t="s">
         <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>182</v>
       </c>
       <c r="B24" t="s">
         <v>188</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="16" t="s">
         <v>189</v>
       </c>
       <c r="D24" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>182</v>
       </c>
       <c r="B25" t="s">
         <v>190</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="16" t="s">
         <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>182</v>
       </c>
       <c r="B26" t="s">
         <v>192</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="16" t="s">
         <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>182</v>
       </c>
       <c r="B27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C27" t="s">
-        <v>196</v>
-      </c>
       <c r="D27" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>182</v>
       </c>
       <c r="B28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="C28" t="s">
-        <v>198</v>
-      </c>
       <c r="D28" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>182</v>
       </c>
       <c r="B29" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="C29" t="s">
-        <v>200</v>
-      </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" t="s">
-        <v>202</v>
+        <v>263</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
-      </c>
-      <c r="C31" t="s">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>201</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>182</v>
       </c>
       <c r="B32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C32" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" t="s">
-        <v>231</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>216</v>
+      <c r="D33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>261</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>261</v>
+      </c>
+      <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>261</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>262</v>
+      </c>
+      <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>262</v>
+      </c>
+      <c r="B41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>262</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3655,9 +3906,9 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3671,7 +3922,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>139</v>
       </c>
@@ -3679,13 +3930,13 @@
         <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>139</v>
       </c>
@@ -3696,10 +3947,10 @@
         <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -3710,7 +3961,7 @@
         <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3724,9 +3975,9 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3740,9 +3991,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
         <v>172</v>
@@ -3751,12 +4002,12 @@
         <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B3" t="s">
         <v>173</v>
@@ -3765,12 +4016,12 @@
         <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
         <v>174</v>
@@ -3779,7 +4030,7 @@
         <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3793,13 +4044,13 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="1"/>
-    <col min="3" max="3" width="43.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3813,46 +4064,46 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
         <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3863,14 +4114,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E295E9-2EFB-493A-8F35-D97F25C99325}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3881,7 +4132,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>151</v>
       </c>
@@ -3892,7 +4143,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>151</v>
       </c>
@@ -3903,7 +4154,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>151</v>
       </c>
@@ -3914,7 +4165,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>151</v>
       </c>
@@ -3925,7 +4176,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>151</v>
       </c>
@@ -3936,7 +4187,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
@@ -3947,7 +4198,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>151</v>
       </c>
@@ -3958,7 +4209,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>151</v>
       </c>
@@ -3977,14 +4228,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7295D2-3BEE-484E-81F9-644774D7558D}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.3984375" customWidth="1"/>
-    <col min="2" max="2" width="19.265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.46484375" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3995,7 +4246,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>161</v>
       </c>
@@ -4006,7 +4257,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
@@ -4017,7 +4268,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>161</v>
       </c>
@@ -4028,7 +4279,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>161</v>
       </c>
@@ -4039,7 +4290,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>161</v>
       </c>
@@ -4050,7 +4301,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>161</v>
       </c>
@@ -4061,7 +4312,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>161</v>
       </c>
@@ -4072,7 +4323,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>161</v>
       </c>
@@ -4094,16 +4345,16 @@
     <tabColor theme="0" tint="-0.14999847407452621"/>
   </sheetPr>
   <dimension ref="A1:F217"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.86328125" customWidth="1"/>
-    <col min="3" max="3" width="26.59765625" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.265625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4114,18 +4365,18 @@
         <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E1" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B2" t="s">
         <v>152</v>
@@ -4134,12 +4385,12 @@
         <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
         <v>153</v>
@@ -4148,12 +4399,12 @@
         <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
         <v>154</v>
@@ -4162,10 +4413,10 @@
         <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -4177,13 +4428,13 @@
         <v>Store # - 10031</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>152</v>
       </c>
@@ -4195,13 +4446,13 @@
         <v>Store # - 10201</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>152</v>
       </c>
@@ -4213,13 +4464,13 @@
         <v>Store # - 10202</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="F7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -4231,13 +4482,13 @@
         <v>Store # - 10203</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>152</v>
       </c>
@@ -4249,7 +4500,7 @@
         <v>Store # - 10204</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -4261,7 +4512,7 @@
         <v>Store # - 10205</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -4273,7 +4524,7 @@
         <v>Store # - 10206</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>152</v>
       </c>
@@ -4285,7 +4536,7 @@
         <v>Store # - 10207</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -4297,7 +4548,7 @@
         <v>Store # - 10208</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>152</v>
       </c>
@@ -4309,7 +4560,7 @@
         <v>Store # - 10210</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -4321,7 +4572,7 @@
         <v>Store # - 10211</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -4333,7 +4584,7 @@
         <v>Store # - 10217</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>152</v>
       </c>
@@ -4345,7 +4596,7 @@
         <v>Store # - 10401</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>152</v>
       </c>
@@ -4357,7 +4608,7 @@
         <v>Store # - 10402</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>152</v>
       </c>
@@ -4369,7 +4620,7 @@
         <v>Store # - 10403</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -4381,7 +4632,7 @@
         <v>Store # - 10404</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -4393,7 +4644,7 @@
         <v>Store # - 10405</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -4405,7 +4656,7 @@
         <v>Store # - 10406</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>152</v>
       </c>
@@ -4417,7 +4668,7 @@
         <v>Store # - 10409</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -4429,7 +4680,7 @@
         <v>Store # - 10410</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>152</v>
       </c>
@@ -4441,7 +4692,7 @@
         <v>Store # - 10411</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -4453,7 +4704,7 @@
         <v>Store # - 10412</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>152</v>
       </c>
@@ -4465,7 +4716,7 @@
         <v>Store # - 10413</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>152</v>
       </c>
@@ -4477,7 +4728,7 @@
         <v>Store # - 10414</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>152</v>
       </c>
@@ -4489,7 +4740,7 @@
         <v>Store # - 10415</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>152</v>
       </c>
@@ -4501,7 +4752,7 @@
         <v>Store # - 10417</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>152</v>
       </c>
@@ -4513,7 +4764,7 @@
         <v>Store # - 10418</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -4525,7 +4776,7 @@
         <v>Store # - 10419</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>152</v>
       </c>
@@ -4537,7 +4788,7 @@
         <v>Store # - 10420</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>152</v>
       </c>
@@ -4549,7 +4800,7 @@
         <v>Store # - 10421</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>152</v>
       </c>
@@ -4561,7 +4812,7 @@
         <v>Store # - 10422</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -4573,7 +4824,7 @@
         <v>Store # - 10423</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -4585,7 +4836,7 @@
         <v>Store # - 10424</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>152</v>
       </c>
@@ -4597,7 +4848,7 @@
         <v>Store # - 10425</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>152</v>
       </c>
@@ -4609,7 +4860,7 @@
         <v>Store # - 10426</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>152</v>
       </c>
@@ -4621,7 +4872,7 @@
         <v>Store # - 10427</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>152</v>
       </c>
@@ -4633,7 +4884,7 @@
         <v>Store # - 10428</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>152</v>
       </c>
@@ -4645,7 +4896,7 @@
         <v>Store # - 10429</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>152</v>
       </c>
@@ -4657,7 +4908,7 @@
         <v>Store # - 10432</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>152</v>
       </c>
@@ -4669,7 +4920,7 @@
         <v>Store # - 10434</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -4681,7 +4932,7 @@
         <v>Store # - 10457</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>152</v>
       </c>
@@ -4693,7 +4944,7 @@
         <v>Store # - 10458</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>153</v>
       </c>
@@ -4705,7 +4956,7 @@
         <v>Store # - 11507</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>153</v>
       </c>
@@ -4717,7 +4968,7 @@
         <v>Store # - 11508</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -4729,7 +4980,7 @@
         <v>Store # - 11511</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>153</v>
       </c>
@@ -4741,7 +4992,7 @@
         <v>Store # - 11512</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>153</v>
       </c>
@@ -4753,7 +5004,7 @@
         <v>Store # - 11513</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -4765,7 +5016,7 @@
         <v>Store # - 11519</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -4777,7 +5028,7 @@
         <v>Store # - 11523</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -4789,7 +5040,7 @@
         <v>Store # - 11524</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>153</v>
       </c>
@@ -4801,7 +5052,7 @@
         <v>Store # - 11525</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>153</v>
       </c>
@@ -4813,7 +5064,7 @@
         <v>Store # - 11526</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -4825,7 +5076,7 @@
         <v>Store # - 11527</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>153</v>
       </c>
@@ -4837,7 +5088,7 @@
         <v>Store # - 11528</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>153</v>
       </c>
@@ -4849,7 +5100,7 @@
         <v>Store # - 11529</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>153</v>
       </c>
@@ -4861,7 +5112,7 @@
         <v>Store # - 11608</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>153</v>
       </c>
@@ -4873,7 +5124,7 @@
         <v>Store # - 11609</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -4885,7 +5136,7 @@
         <v>Store # - 11610</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -4897,7 +5148,7 @@
         <v>Store # - 11611</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>153</v>
       </c>
@@ -4909,7 +5160,7 @@
         <v>Store # - 11612</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>153</v>
       </c>
@@ -4921,7 +5172,7 @@
         <v>Store # - 11613</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>153</v>
       </c>
@@ -4933,7 +5184,7 @@
         <v>Store # - 11614</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>153</v>
       </c>
@@ -4945,7 +5196,7 @@
         <v>Store # - 11615</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>153</v>
       </c>
@@ -4957,7 +5208,7 @@
         <v>Store # - 11616</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -4969,7 +5220,7 @@
         <v>Store # - 11617</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>153</v>
       </c>
@@ -4981,7 +5232,7 @@
         <v>Store # - 11618</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -4993,7 +5244,7 @@
         <v>Store # - 11619</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -5005,7 +5256,7 @@
         <v>Store # - 11620</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>153</v>
       </c>
@@ -5017,7 +5268,7 @@
         <v>Store # - 11621</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>153</v>
       </c>
@@ -5029,7 +5280,7 @@
         <v>Store # - 11622</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -5041,7 +5292,7 @@
         <v>Store # - 11624</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -5053,7 +5304,7 @@
         <v>Store # - 11625</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -5065,7 +5316,7 @@
         <v>Store # - 11709</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>153</v>
       </c>
@@ -5077,7 +5328,7 @@
         <v>Store # - 11717</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>153</v>
       </c>
@@ -5089,7 +5340,7 @@
         <v>Store # - 11718</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>153</v>
       </c>
@@ -5101,7 +5352,7 @@
         <v>Store # - 11719</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>153</v>
       </c>
@@ -5113,7 +5364,7 @@
         <v>Store # - 11720</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>153</v>
       </c>
@@ -5125,7 +5376,7 @@
         <v>Store # - 11723</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -5137,7 +5388,7 @@
         <v>Store # - 11724</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>153</v>
       </c>
@@ -5149,7 +5400,7 @@
         <v>Store # - 11727</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>153</v>
       </c>
@@ -5161,7 +5412,7 @@
         <v>Store # - 11728</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -5173,7 +5424,7 @@
         <v>Store # - 11729</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>153</v>
       </c>
@@ -5185,7 +5436,7 @@
         <v>Store # - 11731</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>153</v>
       </c>
@@ -5197,7 +5448,7 @@
         <v>Store # - 11732</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>153</v>
       </c>
@@ -5209,7 +5460,7 @@
         <v>Store # - 11733</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>153</v>
       </c>
@@ -5221,7 +5472,7 @@
         <v>Store # - 11734</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>153</v>
       </c>
@@ -5233,7 +5484,7 @@
         <v>Store # - 11739</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>153</v>
       </c>
@@ -5245,7 +5496,7 @@
         <v>Store # - 11740</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>153</v>
       </c>
@@ -5257,7 +5508,7 @@
         <v>Store # - 11742</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>153</v>
       </c>
@@ -5269,7 +5520,7 @@
         <v>Store # - 11743</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>153</v>
       </c>
@@ -5281,7 +5532,7 @@
         <v>Store # - 11746</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>153</v>
       </c>
@@ -5293,7 +5544,7 @@
         <v>Store # - 11747</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -5305,7 +5556,7 @@
         <v>Store # - 11749</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -5317,7 +5568,7 @@
         <v>Store # - 11751</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>153</v>
       </c>
@@ -5329,7 +5580,7 @@
         <v>Store # - 11752</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>153</v>
       </c>
@@ -5341,7 +5592,7 @@
         <v>Store # - 11753</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>153</v>
       </c>
@@ -5353,7 +5604,7 @@
         <v>Store # - 11754</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>153</v>
       </c>
@@ -5365,7 +5616,7 @@
         <v>Store # - 11755</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>153</v>
       </c>
@@ -5377,7 +5628,7 @@
         <v>Store # - 11756</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>153</v>
       </c>
@@ -5389,7 +5640,7 @@
         <v>Store # - 11757</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>153</v>
       </c>
@@ -5401,7 +5652,7 @@
         <v>Store # - 11758</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>153</v>
       </c>
@@ -5413,7 +5664,7 @@
         <v>Store # - 11759</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>153</v>
       </c>
@@ -5425,7 +5676,7 @@
         <v>Store # - 11760</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>153</v>
       </c>
@@ -5437,7 +5688,7 @@
         <v>Store # - 11761</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -5449,7 +5700,7 @@
         <v>Store # - 11762</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>153</v>
       </c>
@@ -5461,7 +5712,7 @@
         <v>Store # - 11763</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>153</v>
       </c>
@@ -5473,7 +5724,7 @@
         <v>Store # - 11765</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>153</v>
       </c>
@@ -5485,7 +5736,7 @@
         <v>Store # - 11767</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>153</v>
       </c>
@@ -5497,7 +5748,7 @@
         <v>Store # - 11775</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>153</v>
       </c>
@@ -5509,7 +5760,7 @@
         <v>Store # - 11783</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>153</v>
       </c>
@@ -5521,7 +5772,7 @@
         <v>Store # - 11784</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>153</v>
       </c>
@@ -5533,7 +5784,7 @@
         <v>Store # - 11785</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>153</v>
       </c>
@@ -5545,7 +5796,7 @@
         <v>Store # - 11790</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -5557,7 +5808,7 @@
         <v>Store # - 11792</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>153</v>
       </c>
@@ -5569,7 +5820,7 @@
         <v>Store # - 11800</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>153</v>
       </c>
@@ -5581,7 +5832,7 @@
         <v>Store # - 11891</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>153</v>
       </c>
@@ -5593,7 +5844,7 @@
         <v>Store # - 11894</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>154</v>
       </c>
@@ -5605,7 +5856,7 @@
         <v>Store # - 12102</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>154</v>
       </c>
@@ -5617,7 +5868,7 @@
         <v>Store # - 12105</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>154</v>
       </c>
@@ -5629,7 +5880,7 @@
         <v>Store # - 12108</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>154</v>
       </c>
@@ -5641,7 +5892,7 @@
         <v>Store # - 12111</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -5653,7 +5904,7 @@
         <v>Store # - 12112</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -5665,7 +5916,7 @@
         <v>Store # - 12113</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>154</v>
       </c>
@@ -5677,7 +5928,7 @@
         <v>Store # - 12116</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>154</v>
       </c>
@@ -5689,7 +5940,7 @@
         <v>Store # - 12119</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>154</v>
       </c>
@@ -5701,7 +5952,7 @@
         <v>Store # - 12120</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>154</v>
       </c>
@@ -5713,7 +5964,7 @@
         <v>Store # - 12121</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>154</v>
       </c>
@@ -5725,7 +5976,7 @@
         <v>Store # - 12122</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>154</v>
       </c>
@@ -5737,7 +5988,7 @@
         <v>Store # - 12123</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>154</v>
       </c>
@@ -5749,7 +6000,7 @@
         <v>Store # - 12200</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>154</v>
       </c>
@@ -5761,7 +6012,7 @@
         <v>Store # - 12201</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -5773,7 +6024,7 @@
         <v>Store # - 12205</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -5785,7 +6036,7 @@
         <v>Store # - 12206</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -5797,7 +6048,7 @@
         <v>Store # - 12207</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -5809,7 +6060,7 @@
         <v>Store # - 12208</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -5821,7 +6072,7 @@
         <v>Store # - 12209</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -5833,7 +6084,7 @@
         <v>Store # - 12212</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>154</v>
       </c>
@@ -5845,7 +6096,7 @@
         <v>Store # - 12214</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>154</v>
       </c>
@@ -5857,7 +6108,7 @@
         <v>Store # - 12215</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>154</v>
       </c>
@@ -5869,7 +6120,7 @@
         <v>Store # - 12222</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>154</v>
       </c>
@@ -5881,7 +6132,7 @@
         <v>Store # - 12233</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>154</v>
       </c>
@@ -5893,7 +6144,7 @@
         <v>Store # - 12234</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -5905,7 +6156,7 @@
         <v>Store # - 12236</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>154</v>
       </c>
@@ -5917,7 +6168,7 @@
         <v>Store # - 12237</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>154</v>
       </c>
@@ -5929,7 +6180,7 @@
         <v>Store # - 12238</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -5941,7 +6192,7 @@
         <v>Store # - 12300</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -5953,7 +6204,7 @@
         <v>Store # - 12301</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -5965,7 +6216,7 @@
         <v>Store # - 12302</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>154</v>
       </c>
@@ -5977,7 +6228,7 @@
         <v>Store # - 12303</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -5989,7 +6240,7 @@
         <v>Store # - 12304</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>154</v>
       </c>
@@ -6001,7 +6252,7 @@
         <v>Store # - 12305</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -6013,7 +6264,7 @@
         <v>Store # - 12306</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>154</v>
       </c>
@@ -6025,7 +6276,7 @@
         <v>Store # - 12307</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>154</v>
       </c>
@@ -6037,7 +6288,7 @@
         <v>Store # - 12308</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>154</v>
       </c>
@@ -6049,7 +6300,7 @@
         <v>Store # - 12309</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>154</v>
       </c>
@@ -6061,7 +6312,7 @@
         <v>Store # - 12310</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>154</v>
       </c>
@@ -6073,7 +6324,7 @@
         <v>Store # - 12311</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>154</v>
       </c>
@@ -6085,7 +6336,7 @@
         <v>Store # - 12312</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>154</v>
       </c>
@@ -6097,7 +6348,7 @@
         <v>Store # - 12313</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>154</v>
       </c>
@@ -6109,7 +6360,7 @@
         <v>Store # - 12314</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>154</v>
       </c>
@@ -6121,7 +6372,7 @@
         <v>Store # - 12316</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>154</v>
       </c>
@@ -6133,7 +6384,7 @@
         <v>Store # - 12317</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>154</v>
       </c>
@@ -6145,7 +6396,7 @@
         <v>Store # - 12331</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>154</v>
       </c>
@@ -6157,7 +6408,7 @@
         <v>Store # - 12332</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>154</v>
       </c>
@@ -6169,7 +6420,7 @@
         <v>Store # - 12503</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>154</v>
       </c>
@@ -6181,7 +6432,7 @@
         <v>Store # - 12505</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>154</v>
       </c>
@@ -6193,7 +6444,7 @@
         <v>Store # - 12506</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>154</v>
       </c>
@@ -6205,7 +6456,7 @@
         <v>Store # - 12507</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>154</v>
       </c>
@@ -6217,7 +6468,7 @@
         <v>Store # - 12508</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>154</v>
       </c>
@@ -6229,7 +6480,7 @@
         <v>Store # - 12511</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>154</v>
       </c>
@@ -6241,7 +6492,7 @@
         <v>Store # - 12512</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>154</v>
       </c>
@@ -6253,7 +6504,7 @@
         <v>Store # - 12513</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>154</v>
       </c>
@@ -6265,7 +6516,7 @@
         <v>Store # - 12514</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>154</v>
       </c>
@@ -6277,7 +6528,7 @@
         <v>Store # - 12515</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>154</v>
       </c>
@@ -6289,7 +6540,7 @@
         <v>Store # - 12516</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>154</v>
       </c>
@@ -6301,7 +6552,7 @@
         <v>Store # - 12517</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>154</v>
       </c>
@@ -6313,7 +6564,7 @@
         <v>Store # - 12518</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>154</v>
       </c>
@@ -6325,7 +6576,7 @@
         <v>Store # - 12519</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>154</v>
       </c>
@@ -6337,7 +6588,7 @@
         <v>Store # - 12520</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>154</v>
       </c>
@@ -6349,7 +6600,7 @@
         <v>Store # - 12526</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>154</v>
       </c>
@@ -6361,7 +6612,7 @@
         <v>Store # - 12600</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>154</v>
       </c>
@@ -6373,7 +6624,7 @@
         <v>Store # - 12604</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>154</v>
       </c>
@@ -6385,7 +6636,7 @@
         <v>Store # - 12605</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>154</v>
       </c>
@@ -6397,7 +6648,7 @@
         <v>Store # - 12800</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>154</v>
       </c>
@@ -6409,7 +6660,7 @@
         <v>Store # - 12801</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>154</v>
       </c>
@@ -6421,7 +6672,7 @@
         <v>Store # - 12802</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>154</v>
       </c>
@@ -6433,7 +6684,7 @@
         <v>Store # - 12803</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>154</v>
       </c>
@@ -6445,7 +6696,7 @@
         <v>Store # - 12804</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>154</v>
       </c>
@@ -6457,7 +6708,7 @@
         <v>Store # - 12805</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>154</v>
       </c>
@@ -6469,7 +6720,7 @@
         <v>Store # - 12806</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>154</v>
       </c>
@@ -6481,7 +6732,7 @@
         <v>Store # - 12808</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>154</v>
       </c>
@@ -6493,7 +6744,7 @@
         <v>Store # - 12809</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>154</v>
       </c>
@@ -6505,7 +6756,7 @@
         <v>Store # - 12810</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>154</v>
       </c>
@@ -6517,7 +6768,7 @@
         <v>Store # - 12811</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>154</v>
       </c>
@@ -6529,7 +6780,7 @@
         <v>Store # - 12812</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>154</v>
       </c>
@@ -6541,7 +6792,7 @@
         <v>Store # - 12813</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>154</v>
       </c>
@@ -6553,7 +6804,7 @@
         <v>Store # - 12814</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>154</v>
       </c>
@@ -6565,7 +6816,7 @@
         <v>Store # - 12815</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>154</v>
       </c>
@@ -6577,7 +6828,7 @@
         <v>Store # - 12816</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>154</v>
       </c>
@@ -6589,7 +6840,7 @@
         <v>Store # - 12817</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>154</v>
       </c>
@@ -6601,7 +6852,7 @@
         <v>Store # - 12819</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>154</v>
       </c>
@@ -6613,7 +6864,7 @@
         <v>Store # - 12820</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>154</v>
       </c>
@@ -6625,7 +6876,7 @@
         <v>Store # - 12821</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>154</v>
       </c>
@@ -6637,7 +6888,7 @@
         <v>Store # - 12822</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>154</v>
       </c>
@@ -6649,7 +6900,7 @@
         <v>Store # - 12823</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>154</v>
       </c>
@@ -6661,7 +6912,7 @@
         <v>Store # - 12824</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>154</v>
       </c>
@@ -6673,7 +6924,7 @@
         <v>Store # - 12825</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>154</v>
       </c>
@@ -6685,7 +6936,7 @@
         <v>Store # - 12826</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>154</v>
       </c>
@@ -6697,7 +6948,7 @@
         <v>Store # - 12832</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>154</v>
       </c>
@@ -6709,7 +6960,7 @@
         <v>Store # - 12833</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>154</v>
       </c>
@@ -6721,7 +6972,7 @@
         <v>Store # - 12834</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>154</v>
       </c>
@@ -6733,7 +6984,7 @@
         <v>Store # - 12835</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>154</v>
       </c>
